--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>200</v>
       </c>
       <c r="D2" t="str">
-        <v>47 ms</v>
+        <v>43 ms</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T12:43:57.340Z</v>
+        <v>2026-07-29T13:05:24.644Z</v>
       </c>
       <c r="F2" t="str">
         <v>Baseline request succeeded</v>

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>42454</v>
+        <v>86310</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>707.57</v>
+        <v>1438.5</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>707.57</v>
+        <v>1438.5</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>141.3</v>
+        <v>69.49</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>531</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>380</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>431</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>141.3</v>
+        <v>69.49</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>531</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>380</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>431</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>707.57</v>
+        <v>1438.5</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>89020</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>1483.67</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>1483.67</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>67.36</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>155</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>91</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>67.36</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>155</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>91</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>1483.67</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L401"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -706,7 +706,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H3" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I3" t="str">
         <v>Medium</v>
@@ -718,7 +718,7 @@
         <v>Automated</v>
       </c>
       <c r="L3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H4" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I4" t="str">
         <v>Medium</v>
@@ -756,7 +756,7 @@
         <v>Automated</v>
       </c>
       <c r="L4" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="5">
@@ -820,7 +820,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H6" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I6" t="str">
         <v>High</v>
@@ -832,7 +832,7 @@
         <v>Automated</v>
       </c>
       <c r="L6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="7">
@@ -858,7 +858,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H7" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I7" t="str">
         <v>Medium</v>
@@ -870,7 +870,7 @@
         <v>Automated</v>
       </c>
       <c r="L7" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H9" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I9" t="str">
         <v>Medium</v>
@@ -946,7 +946,7 @@
         <v>Automated</v>
       </c>
       <c r="L9" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="10">
@@ -972,7 +972,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H10" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I10" t="str">
         <v>High</v>
@@ -984,7 +984,7 @@
         <v>Automated</v>
       </c>
       <c r="L10" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="11">
@@ -1048,7 +1048,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H12" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I12" t="str">
         <v>Medium</v>
@@ -1060,7 +1060,7 @@
         <v>Automated</v>
       </c>
       <c r="L12" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="13">
@@ -1086,7 +1086,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H13" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I13" t="str">
         <v>Medium</v>
@@ -1098,7 +1098,7 @@
         <v>Automated</v>
       </c>
       <c r="L13" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="14">
@@ -1162,7 +1162,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H15" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I15" t="str">
         <v>Medium</v>
@@ -1174,7 +1174,7 @@
         <v>Automated</v>
       </c>
       <c r="L15" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="16">
@@ -1200,7 +1200,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H16" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I16" t="str">
         <v>Medium</v>
@@ -1212,7 +1212,7 @@
         <v>Automated</v>
       </c>
       <c r="L16" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H18" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I18" t="str">
         <v>High</v>
@@ -1288,7 +1288,7 @@
         <v>Automated</v>
       </c>
       <c r="L18" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="19">
@@ -1314,7 +1314,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H19" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I19" t="str">
         <v>Medium</v>
@@ -1326,7 +1326,7 @@
         <v>Automated</v>
       </c>
       <c r="L19" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="20">
@@ -1390,7 +1390,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H21" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I21" t="str">
         <v>Medium</v>
@@ -1402,7 +1402,7 @@
         <v>Automated</v>
       </c>
       <c r="L21" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="22">
@@ -1428,7 +1428,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H22" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I22" t="str">
         <v>High</v>
@@ -1440,7 +1440,7 @@
         <v>Automated</v>
       </c>
       <c r="L22" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="23">
@@ -1504,7 +1504,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H24" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I24" t="str">
         <v>Medium</v>
@@ -1516,7 +1516,7 @@
         <v>Automated</v>
       </c>
       <c r="L24" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="25">
@@ -1542,7 +1542,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H25" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I25" t="str">
         <v>Medium</v>
@@ -1554,7 +1554,7 @@
         <v>Automated</v>
       </c>
       <c r="L25" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H27" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I27" t="str">
         <v>Medium</v>
@@ -1630,7 +1630,7 @@
         <v>Automated</v>
       </c>
       <c r="L27" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="28">
@@ -1656,7 +1656,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H28" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I28" t="str">
         <v>Medium</v>
@@ -1668,7 +1668,7 @@
         <v>Automated</v>
       </c>
       <c r="L28" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="29">
@@ -1732,7 +1732,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H30" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I30" t="str">
         <v>High</v>
@@ -1744,7 +1744,7 @@
         <v>Automated</v>
       </c>
       <c r="L30" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="31">
@@ -1770,7 +1770,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H31" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I31" t="str">
         <v>Medium</v>
@@ -1782,7 +1782,7 @@
         <v>Automated</v>
       </c>
       <c r="L31" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="32">
@@ -1846,7 +1846,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H33" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I33" t="str">
         <v>Medium</v>
@@ -1858,7 +1858,7 @@
         <v>Automated</v>
       </c>
       <c r="L33" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="34">
@@ -1884,7 +1884,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H34" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I34" t="str">
         <v>High</v>
@@ -1896,7 +1896,7 @@
         <v>Automated</v>
       </c>
       <c r="L34" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="35">
@@ -1960,7 +1960,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H36" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I36" t="str">
         <v>Medium</v>
@@ -1972,7 +1972,7 @@
         <v>Automated</v>
       </c>
       <c r="L36" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="37">
@@ -1998,7 +1998,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H37" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I37" t="str">
         <v>Medium</v>
@@ -2010,7 +2010,7 @@
         <v>Automated</v>
       </c>
       <c r="L37" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="38">
@@ -2074,7 +2074,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H39" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I39" t="str">
         <v>Medium</v>
@@ -2086,7 +2086,7 @@
         <v>Automated</v>
       </c>
       <c r="L39" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="40">
@@ -2112,7 +2112,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H40" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I40" t="str">
         <v>Medium</v>
@@ -2124,7 +2124,7 @@
         <v>Automated</v>
       </c>
       <c r="L40" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="41">
@@ -2188,7 +2188,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H42" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I42" t="str">
         <v>High</v>
@@ -2200,7 +2200,7 @@
         <v>Automated</v>
       </c>
       <c r="L42" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="43">
@@ -2226,7 +2226,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H43" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I43" t="str">
         <v>Medium</v>
@@ -2238,7 +2238,7 @@
         <v>Automated</v>
       </c>
       <c r="L43" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="44">
@@ -2302,7 +2302,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H45" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I45" t="str">
         <v>Medium</v>
@@ -2314,7 +2314,7 @@
         <v>Automated</v>
       </c>
       <c r="L45" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="46">
@@ -2340,7 +2340,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H46" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I46" t="str">
         <v>High</v>
@@ -2352,7 +2352,7 @@
         <v>Automated</v>
       </c>
       <c r="L46" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="47">
@@ -2416,7 +2416,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H48" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I48" t="str">
         <v>Medium</v>
@@ -2428,7 +2428,7 @@
         <v>Automated</v>
       </c>
       <c r="L48" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="49">
@@ -2454,7 +2454,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H49" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I49" t="str">
         <v>Medium</v>
@@ -2466,7 +2466,7 @@
         <v>Automated</v>
       </c>
       <c r="L49" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="50">
@@ -2530,7 +2530,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H51" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I51" t="str">
         <v>Medium</v>
@@ -2542,7 +2542,7 @@
         <v>Automated</v>
       </c>
       <c r="L51" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="52">
@@ -2568,7 +2568,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H52" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I52" t="str">
         <v>Medium</v>
@@ -2580,7 +2580,7 @@
         <v>Automated</v>
       </c>
       <c r="L52" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="53">
@@ -2644,7 +2644,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H54" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I54" t="str">
         <v>High</v>
@@ -2656,7 +2656,7 @@
         <v>Automated</v>
       </c>
       <c r="L54" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="55">
@@ -2682,7 +2682,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H55" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I55" t="str">
         <v>Medium</v>
@@ -2694,7 +2694,7 @@
         <v>Automated</v>
       </c>
       <c r="L55" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="56">
@@ -2758,7 +2758,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H57" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I57" t="str">
         <v>Medium</v>
@@ -2770,7 +2770,7 @@
         <v>Automated</v>
       </c>
       <c r="L57" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="58">
@@ -2796,7 +2796,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H58" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I58" t="str">
         <v>High</v>
@@ -2808,7 +2808,7 @@
         <v>Automated</v>
       </c>
       <c r="L58" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="59">
@@ -2872,7 +2872,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H60" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I60" t="str">
         <v>Medium</v>
@@ -2884,7 +2884,7 @@
         <v>Automated</v>
       </c>
       <c r="L60" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="61">
@@ -2910,7 +2910,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H61" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I61" t="str">
         <v>Medium</v>
@@ -2922,7 +2922,7 @@
         <v>Automated</v>
       </c>
       <c r="L61" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="62">
@@ -2986,7 +2986,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H63" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I63" t="str">
         <v>Medium</v>
@@ -2998,7 +2998,7 @@
         <v>Automated</v>
       </c>
       <c r="L63" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="64">
@@ -3024,7 +3024,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H64" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I64" t="str">
         <v>Medium</v>
@@ -3036,7 +3036,7 @@
         <v>Automated</v>
       </c>
       <c r="L64" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="65">
@@ -3100,7 +3100,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H66" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I66" t="str">
         <v>High</v>
@@ -3112,7 +3112,7 @@
         <v>Automated</v>
       </c>
       <c r="L66" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="67">
@@ -3138,7 +3138,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H67" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I67" t="str">
         <v>Medium</v>
@@ -3150,7 +3150,7 @@
         <v>Automated</v>
       </c>
       <c r="L67" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="68">
@@ -3214,7 +3214,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H69" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I69" t="str">
         <v>Medium</v>
@@ -3226,7 +3226,7 @@
         <v>Automated</v>
       </c>
       <c r="L69" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="70">
@@ -3252,7 +3252,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H70" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I70" t="str">
         <v>High</v>
@@ -3264,7 +3264,7 @@
         <v>Automated</v>
       </c>
       <c r="L70" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="71">
@@ -3328,7 +3328,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H72" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I72" t="str">
         <v>Medium</v>
@@ -3340,7 +3340,7 @@
         <v>Automated</v>
       </c>
       <c r="L72" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="73">
@@ -3366,7 +3366,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H73" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I73" t="str">
         <v>Medium</v>
@@ -3378,7 +3378,7 @@
         <v>Automated</v>
       </c>
       <c r="L73" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="74">
@@ -3442,7 +3442,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H75" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I75" t="str">
         <v>Medium</v>
@@ -3454,7 +3454,7 @@
         <v>Automated</v>
       </c>
       <c r="L75" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="76">
@@ -3480,7 +3480,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H76" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I76" t="str">
         <v>Medium</v>
@@ -3492,7 +3492,7 @@
         <v>Automated</v>
       </c>
       <c r="L76" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="77">
@@ -3556,7 +3556,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H78" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I78" t="str">
         <v>High</v>
@@ -3568,7 +3568,7 @@
         <v>Automated</v>
       </c>
       <c r="L78" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="79">
@@ -3594,7 +3594,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H79" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I79" t="str">
         <v>Medium</v>
@@ -3606,7 +3606,7 @@
         <v>Automated</v>
       </c>
       <c r="L79" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="80">
@@ -3670,7 +3670,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H81" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I81" t="str">
         <v>Medium</v>
@@ -3682,7 +3682,7 @@
         <v>Automated</v>
       </c>
       <c r="L81" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="82">
@@ -3708,7 +3708,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H82" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I82" t="str">
         <v>High</v>
@@ -3720,7 +3720,7 @@
         <v>Automated</v>
       </c>
       <c r="L82" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="83">
@@ -3784,7 +3784,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H84" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I84" t="str">
         <v>Medium</v>
@@ -3796,7 +3796,7 @@
         <v>Automated</v>
       </c>
       <c r="L84" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="85">
@@ -3822,7 +3822,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H85" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I85" t="str">
         <v>Medium</v>
@@ -3834,7 +3834,7 @@
         <v>Automated</v>
       </c>
       <c r="L85" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="86">
@@ -3898,7 +3898,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H87" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I87" t="str">
         <v>Medium</v>
@@ -3910,7 +3910,7 @@
         <v>Automated</v>
       </c>
       <c r="L87" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="88">
@@ -3936,7 +3936,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H88" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I88" t="str">
         <v>Medium</v>
@@ -3948,7 +3948,7 @@
         <v>Automated</v>
       </c>
       <c r="L88" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="89">
@@ -4012,7 +4012,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H90" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I90" t="str">
         <v>High</v>
@@ -4024,7 +4024,7 @@
         <v>Automated</v>
       </c>
       <c r="L90" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="91">
@@ -4050,7 +4050,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H91" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I91" t="str">
         <v>Medium</v>
@@ -4062,7 +4062,7 @@
         <v>Automated</v>
       </c>
       <c r="L91" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="92">
@@ -4126,7 +4126,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H93" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I93" t="str">
         <v>Medium</v>
@@ -4138,7 +4138,7 @@
         <v>Automated</v>
       </c>
       <c r="L93" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="94">
@@ -4164,7 +4164,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H94" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I94" t="str">
         <v>High</v>
@@ -4176,7 +4176,7 @@
         <v>Automated</v>
       </c>
       <c r="L94" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="95">
@@ -4240,7 +4240,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H96" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I96" t="str">
         <v>Medium</v>
@@ -4252,7 +4252,7 @@
         <v>Automated</v>
       </c>
       <c r="L96" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="97">
@@ -4278,7 +4278,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H97" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I97" t="str">
         <v>Medium</v>
@@ -4290,7 +4290,7 @@
         <v>Automated</v>
       </c>
       <c r="L97" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="98">
@@ -4354,7 +4354,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H99" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I99" t="str">
         <v>Medium</v>
@@ -4366,7 +4366,7 @@
         <v>Automated</v>
       </c>
       <c r="L99" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="100">
@@ -4392,7 +4392,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H100" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I100" t="str">
         <v>Medium</v>
@@ -4404,7 +4404,7 @@
         <v>Automated</v>
       </c>
       <c r="L100" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="101">
@@ -4468,7 +4468,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H102" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I102" t="str">
         <v>High</v>
@@ -4480,7 +4480,7 @@
         <v>Automated</v>
       </c>
       <c r="L102" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="103">
@@ -4506,7 +4506,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H103" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I103" t="str">
         <v>Medium</v>
@@ -4518,7 +4518,7 @@
         <v>Automated</v>
       </c>
       <c r="L103" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="104">
@@ -4582,7 +4582,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H105" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I105" t="str">
         <v>Medium</v>
@@ -4594,7 +4594,7 @@
         <v>Automated</v>
       </c>
       <c r="L105" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="106">
@@ -4620,7 +4620,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H106" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I106" t="str">
         <v>High</v>
@@ -4632,7 +4632,7 @@
         <v>Automated</v>
       </c>
       <c r="L106" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="107">
@@ -4696,7 +4696,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H108" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I108" t="str">
         <v>Medium</v>
@@ -4708,7 +4708,7 @@
         <v>Automated</v>
       </c>
       <c r="L108" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="109">
@@ -4734,7 +4734,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H109" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I109" t="str">
         <v>Medium</v>
@@ -4746,7 +4746,7 @@
         <v>Automated</v>
       </c>
       <c r="L109" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="110">
@@ -4810,7 +4810,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H111" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I111" t="str">
         <v>Medium</v>
@@ -4822,7 +4822,7 @@
         <v>Automated</v>
       </c>
       <c r="L111" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="112">
@@ -4848,7 +4848,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H112" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I112" t="str">
         <v>Medium</v>
@@ -4860,7 +4860,7 @@
         <v>Automated</v>
       </c>
       <c r="L112" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="113">
@@ -4924,7 +4924,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H114" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I114" t="str">
         <v>High</v>
@@ -4936,7 +4936,7 @@
         <v>Automated</v>
       </c>
       <c r="L114" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="115">
@@ -4962,7 +4962,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H115" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I115" t="str">
         <v>Medium</v>
@@ -4974,7 +4974,7 @@
         <v>Automated</v>
       </c>
       <c r="L115" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="116">
@@ -5038,7 +5038,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H117" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I117" t="str">
         <v>Medium</v>
@@ -5050,7 +5050,7 @@
         <v>Automated</v>
       </c>
       <c r="L117" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="118">
@@ -5076,7 +5076,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H118" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I118" t="str">
         <v>High</v>
@@ -5088,7 +5088,7 @@
         <v>Automated</v>
       </c>
       <c r="L118" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="119">
@@ -5152,7 +5152,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H120" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I120" t="str">
         <v>Medium</v>
@@ -5164,7 +5164,7 @@
         <v>Automated</v>
       </c>
       <c r="L120" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="121">
@@ -5190,7 +5190,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H121" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I121" t="str">
         <v>Medium</v>
@@ -5202,7 +5202,7 @@
         <v>Automated</v>
       </c>
       <c r="L121" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="122">
@@ -5266,7 +5266,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H123" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I123" t="str">
         <v>Medium</v>
@@ -5278,7 +5278,7 @@
         <v>Automated</v>
       </c>
       <c r="L123" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="124">
@@ -5304,7 +5304,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H124" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I124" t="str">
         <v>Medium</v>
@@ -5316,7 +5316,7 @@
         <v>Automated</v>
       </c>
       <c r="L124" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="125">
@@ -5380,7 +5380,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H126" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I126" t="str">
         <v>High</v>
@@ -5392,7 +5392,7 @@
         <v>Automated</v>
       </c>
       <c r="L126" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="127">
@@ -5418,7 +5418,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H127" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I127" t="str">
         <v>Medium</v>
@@ -5430,7 +5430,7 @@
         <v>Automated</v>
       </c>
       <c r="L127" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="128">
@@ -5494,7 +5494,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H129" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I129" t="str">
         <v>Medium</v>
@@ -5506,7 +5506,7 @@
         <v>Automated</v>
       </c>
       <c r="L129" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="130">
@@ -5532,7 +5532,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H130" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I130" t="str">
         <v>High</v>
@@ -5544,7 +5544,7 @@
         <v>Automated</v>
       </c>
       <c r="L130" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="131">
@@ -5608,7 +5608,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H132" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I132" t="str">
         <v>Medium</v>
@@ -5620,7 +5620,7 @@
         <v>Automated</v>
       </c>
       <c r="L132" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="133">
@@ -5646,7 +5646,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H133" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I133" t="str">
         <v>Medium</v>
@@ -5658,7 +5658,7 @@
         <v>Automated</v>
       </c>
       <c r="L133" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="134">
@@ -5722,7 +5722,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H135" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I135" t="str">
         <v>Medium</v>
@@ -5734,7 +5734,7 @@
         <v>Automated</v>
       </c>
       <c r="L135" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="136">
@@ -5760,7 +5760,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H136" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I136" t="str">
         <v>Medium</v>
@@ -5772,7 +5772,7 @@
         <v>Automated</v>
       </c>
       <c r="L136" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="137">
@@ -5836,7 +5836,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H138" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I138" t="str">
         <v>High</v>
@@ -5848,7 +5848,7 @@
         <v>Automated</v>
       </c>
       <c r="L138" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="139">
@@ -5874,7 +5874,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H139" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I139" t="str">
         <v>Medium</v>
@@ -5886,7 +5886,7 @@
         <v>Automated</v>
       </c>
       <c r="L139" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="140">
@@ -5950,7 +5950,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H141" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I141" t="str">
         <v>Medium</v>
@@ -5962,7 +5962,7 @@
         <v>Automated</v>
       </c>
       <c r="L141" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="142">
@@ -5988,7 +5988,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H142" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I142" t="str">
         <v>High</v>
@@ -6000,7 +6000,7 @@
         <v>Automated</v>
       </c>
       <c r="L142" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="143">
@@ -6064,7 +6064,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H144" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I144" t="str">
         <v>Medium</v>
@@ -6076,7 +6076,7 @@
         <v>Automated</v>
       </c>
       <c r="L144" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="145">
@@ -6102,7 +6102,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H145" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I145" t="str">
         <v>Medium</v>
@@ -6114,7 +6114,7 @@
         <v>Automated</v>
       </c>
       <c r="L145" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="146">
@@ -6178,7 +6178,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H147" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I147" t="str">
         <v>Medium</v>
@@ -6190,7 +6190,7 @@
         <v>Automated</v>
       </c>
       <c r="L147" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="148">
@@ -6216,7 +6216,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H148" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I148" t="str">
         <v>Medium</v>
@@ -6228,7 +6228,7 @@
         <v>Automated</v>
       </c>
       <c r="L148" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="149">
@@ -6292,7 +6292,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H150" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I150" t="str">
         <v>High</v>
@@ -6304,7 +6304,7 @@
         <v>Automated</v>
       </c>
       <c r="L150" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="151">
@@ -6330,7 +6330,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H151" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I151" t="str">
         <v>Medium</v>
@@ -6342,7 +6342,7 @@
         <v>Automated</v>
       </c>
       <c r="L151" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="152">
@@ -6406,7 +6406,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H153" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I153" t="str">
         <v>Medium</v>
@@ -6418,7 +6418,7 @@
         <v>Automated</v>
       </c>
       <c r="L153" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="154">
@@ -6444,7 +6444,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H154" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I154" t="str">
         <v>High</v>
@@ -6456,7 +6456,7 @@
         <v>Automated</v>
       </c>
       <c r="L154" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="155">
@@ -6520,7 +6520,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H156" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I156" t="str">
         <v>Medium</v>
@@ -6532,7 +6532,7 @@
         <v>Automated</v>
       </c>
       <c r="L156" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="157">
@@ -6558,7 +6558,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H157" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I157" t="str">
         <v>Medium</v>
@@ -6570,7 +6570,7 @@
         <v>Automated</v>
       </c>
       <c r="L157" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="158">
@@ -6634,7 +6634,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H159" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I159" t="str">
         <v>Medium</v>
@@ -6646,7 +6646,7 @@
         <v>Automated</v>
       </c>
       <c r="L159" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="160">
@@ -6672,7 +6672,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H160" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I160" t="str">
         <v>Medium</v>
@@ -6684,7 +6684,7 @@
         <v>Automated</v>
       </c>
       <c r="L160" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="161">
@@ -6748,7 +6748,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H162" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I162" t="str">
         <v>High</v>
@@ -6760,7 +6760,7 @@
         <v>Automated</v>
       </c>
       <c r="L162" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="163">
@@ -6786,7 +6786,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H163" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I163" t="str">
         <v>Medium</v>
@@ -6798,7 +6798,7 @@
         <v>Automated</v>
       </c>
       <c r="L163" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="164">
@@ -6862,7 +6862,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H165" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I165" t="str">
         <v>Medium</v>
@@ -6874,7 +6874,7 @@
         <v>Automated</v>
       </c>
       <c r="L165" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="166">
@@ -6900,7 +6900,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H166" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I166" t="str">
         <v>High</v>
@@ -6912,7 +6912,7 @@
         <v>Automated</v>
       </c>
       <c r="L166" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="167">
@@ -6976,7 +6976,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H168" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I168" t="str">
         <v>Medium</v>
@@ -6988,7 +6988,7 @@
         <v>Automated</v>
       </c>
       <c r="L168" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="169">
@@ -7014,7 +7014,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H169" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I169" t="str">
         <v>Medium</v>
@@ -7026,7 +7026,7 @@
         <v>Automated</v>
       </c>
       <c r="L169" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="170">
@@ -7090,7 +7090,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H171" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I171" t="str">
         <v>Medium</v>
@@ -7102,7 +7102,7 @@
         <v>Automated</v>
       </c>
       <c r="L171" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="172">
@@ -7128,7 +7128,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H172" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I172" t="str">
         <v>Medium</v>
@@ -7140,7 +7140,7 @@
         <v>Automated</v>
       </c>
       <c r="L172" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="173">
@@ -7204,7 +7204,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H174" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I174" t="str">
         <v>High</v>
@@ -7216,7 +7216,7 @@
         <v>Automated</v>
       </c>
       <c r="L174" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="175">
@@ -7242,7 +7242,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H175" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I175" t="str">
         <v>Medium</v>
@@ -7254,7 +7254,7 @@
         <v>Automated</v>
       </c>
       <c r="L175" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="176">
@@ -7318,7 +7318,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H177" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I177" t="str">
         <v>Medium</v>
@@ -7330,7 +7330,7 @@
         <v>Automated</v>
       </c>
       <c r="L177" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="178">
@@ -7356,7 +7356,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H178" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I178" t="str">
         <v>High</v>
@@ -7368,7 +7368,7 @@
         <v>Automated</v>
       </c>
       <c r="L178" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="179">
@@ -7432,7 +7432,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H180" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I180" t="str">
         <v>Medium</v>
@@ -7444,7 +7444,7 @@
         <v>Automated</v>
       </c>
       <c r="L180" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="181">
@@ -7470,7 +7470,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H181" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I181" t="str">
         <v>Medium</v>
@@ -7482,7 +7482,7 @@
         <v>Automated</v>
       </c>
       <c r="L181" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="182">
@@ -7546,7 +7546,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H183" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I183" t="str">
         <v>Medium</v>
@@ -7558,7 +7558,7 @@
         <v>Automated</v>
       </c>
       <c r="L183" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="184">
@@ -7584,7 +7584,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H184" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I184" t="str">
         <v>Medium</v>
@@ -7596,7 +7596,7 @@
         <v>Automated</v>
       </c>
       <c r="L184" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="185">
@@ -7660,7 +7660,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H186" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I186" t="str">
         <v>High</v>
@@ -7672,7 +7672,7 @@
         <v>Automated</v>
       </c>
       <c r="L186" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="187">
@@ -7698,7 +7698,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H187" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I187" t="str">
         <v>Medium</v>
@@ -7710,7 +7710,7 @@
         <v>Automated</v>
       </c>
       <c r="L187" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="188">
@@ -7774,7 +7774,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H189" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I189" t="str">
         <v>Medium</v>
@@ -7786,7 +7786,7 @@
         <v>Automated</v>
       </c>
       <c r="L189" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="190">
@@ -7812,7 +7812,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H190" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I190" t="str">
         <v>High</v>
@@ -7824,7 +7824,7 @@
         <v>Automated</v>
       </c>
       <c r="L190" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="191">
@@ -7888,7 +7888,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H192" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I192" t="str">
         <v>Medium</v>
@@ -7900,7 +7900,7 @@
         <v>Automated</v>
       </c>
       <c r="L192" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="193">
@@ -7926,7 +7926,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H193" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I193" t="str">
         <v>Medium</v>
@@ -7938,7 +7938,7 @@
         <v>Automated</v>
       </c>
       <c r="L193" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="194">
@@ -8002,7 +8002,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H195" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I195" t="str">
         <v>Medium</v>
@@ -8014,7 +8014,7 @@
         <v>Automated</v>
       </c>
       <c r="L195" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="196">
@@ -8040,7 +8040,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H196" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I196" t="str">
         <v>Medium</v>
@@ -8052,7 +8052,7 @@
         <v>Automated</v>
       </c>
       <c r="L196" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="197">
@@ -8116,7 +8116,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H198" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I198" t="str">
         <v>High</v>
@@ -8128,7 +8128,7 @@
         <v>Automated</v>
       </c>
       <c r="L198" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="199">
@@ -8154,7 +8154,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H199" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I199" t="str">
         <v>Medium</v>
@@ -8166,7 +8166,7 @@
         <v>Automated</v>
       </c>
       <c r="L199" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="200">
@@ -8230,7 +8230,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H201" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I201" t="str">
         <v>Medium</v>
@@ -8242,7 +8242,7 @@
         <v>Automated</v>
       </c>
       <c r="L201" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="202">
@@ -8268,7 +8268,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H202" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I202" t="str">
         <v>High</v>
@@ -8280,7 +8280,7 @@
         <v>Automated</v>
       </c>
       <c r="L202" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="203">
@@ -8344,7 +8344,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H204" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I204" t="str">
         <v>Medium</v>
@@ -8356,7 +8356,7 @@
         <v>Automated</v>
       </c>
       <c r="L204" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="205">
@@ -8382,7 +8382,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H205" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I205" t="str">
         <v>Medium</v>
@@ -8394,7 +8394,7 @@
         <v>Automated</v>
       </c>
       <c r="L205" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="206">
@@ -8458,7 +8458,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H207" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I207" t="str">
         <v>Medium</v>
@@ -8470,7 +8470,7 @@
         <v>Automated</v>
       </c>
       <c r="L207" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="208">
@@ -8496,7 +8496,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H208" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I208" t="str">
         <v>Medium</v>
@@ -8508,7 +8508,7 @@
         <v>Automated</v>
       </c>
       <c r="L208" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="209">
@@ -8572,7 +8572,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H210" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I210" t="str">
         <v>High</v>
@@ -8584,7 +8584,7 @@
         <v>Automated</v>
       </c>
       <c r="L210" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="211">
@@ -8610,7 +8610,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H211" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I211" t="str">
         <v>Medium</v>
@@ -8622,7 +8622,7 @@
         <v>Automated</v>
       </c>
       <c r="L211" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="212">
@@ -8686,7 +8686,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H213" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I213" t="str">
         <v>Medium</v>
@@ -8698,7 +8698,7 @@
         <v>Automated</v>
       </c>
       <c r="L213" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="214">
@@ -8724,7 +8724,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H214" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I214" t="str">
         <v>High</v>
@@ -8736,7 +8736,7 @@
         <v>Automated</v>
       </c>
       <c r="L214" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="215">
@@ -8800,7 +8800,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H216" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I216" t="str">
         <v>Medium</v>
@@ -8812,7 +8812,7 @@
         <v>Automated</v>
       </c>
       <c r="L216" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="217">
@@ -8838,7 +8838,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H217" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I217" t="str">
         <v>Medium</v>
@@ -8850,7 +8850,7 @@
         <v>Automated</v>
       </c>
       <c r="L217" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="218">
@@ -8914,7 +8914,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H219" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I219" t="str">
         <v>Medium</v>
@@ -8926,7 +8926,7 @@
         <v>Automated</v>
       </c>
       <c r="L219" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="220">
@@ -8952,7 +8952,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H220" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I220" t="str">
         <v>Medium</v>
@@ -8964,7 +8964,7 @@
         <v>Automated</v>
       </c>
       <c r="L220" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="221">
@@ -9028,7 +9028,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H222" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I222" t="str">
         <v>High</v>
@@ -9040,7 +9040,7 @@
         <v>Automated</v>
       </c>
       <c r="L222" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="223">
@@ -9066,7 +9066,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H223" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I223" t="str">
         <v>Medium</v>
@@ -9078,7 +9078,7 @@
         <v>Automated</v>
       </c>
       <c r="L223" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="224">
@@ -9142,7 +9142,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H225" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I225" t="str">
         <v>Medium</v>
@@ -9154,7 +9154,7 @@
         <v>Automated</v>
       </c>
       <c r="L225" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="226">
@@ -9180,7 +9180,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H226" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I226" t="str">
         <v>High</v>
@@ -9192,7 +9192,7 @@
         <v>Automated</v>
       </c>
       <c r="L226" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="227">
@@ -9256,7 +9256,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H228" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I228" t="str">
         <v>Medium</v>
@@ -9268,7 +9268,7 @@
         <v>Automated</v>
       </c>
       <c r="L228" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="229">
@@ -9294,7 +9294,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H229" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I229" t="str">
         <v>Medium</v>
@@ -9306,7 +9306,7 @@
         <v>Automated</v>
       </c>
       <c r="L229" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="230">
@@ -9370,7 +9370,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H231" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I231" t="str">
         <v>Medium</v>
@@ -9382,7 +9382,7 @@
         <v>Automated</v>
       </c>
       <c r="L231" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="232">
@@ -9408,7 +9408,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H232" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I232" t="str">
         <v>Medium</v>
@@ -9420,7 +9420,7 @@
         <v>Automated</v>
       </c>
       <c r="L232" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="233">
@@ -9484,7 +9484,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H234" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I234" t="str">
         <v>High</v>
@@ -9496,7 +9496,7 @@
         <v>Automated</v>
       </c>
       <c r="L234" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="235">
@@ -9522,7 +9522,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H235" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I235" t="str">
         <v>Medium</v>
@@ -9534,7 +9534,7 @@
         <v>Automated</v>
       </c>
       <c r="L235" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="236">
@@ -9598,7 +9598,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H237" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I237" t="str">
         <v>Medium</v>
@@ -9610,7 +9610,7 @@
         <v>Automated</v>
       </c>
       <c r="L237" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="238">
@@ -9636,7 +9636,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H238" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I238" t="str">
         <v>High</v>
@@ -9648,7 +9648,7 @@
         <v>Automated</v>
       </c>
       <c r="L238" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="239">
@@ -9712,7 +9712,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H240" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I240" t="str">
         <v>Medium</v>
@@ -9724,7 +9724,7 @@
         <v>Automated</v>
       </c>
       <c r="L240" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="241">
@@ -9750,7 +9750,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H241" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I241" t="str">
         <v>Medium</v>
@@ -9762,7 +9762,7 @@
         <v>Automated</v>
       </c>
       <c r="L241" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="242">
@@ -9826,7 +9826,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H243" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I243" t="str">
         <v>Medium</v>
@@ -9838,7 +9838,7 @@
         <v>Automated</v>
       </c>
       <c r="L243" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="244">
@@ -9864,7 +9864,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H244" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I244" t="str">
         <v>Medium</v>
@@ -9876,7 +9876,7 @@
         <v>Automated</v>
       </c>
       <c r="L244" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="245">
@@ -9940,7 +9940,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H246" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I246" t="str">
         <v>High</v>
@@ -9952,7 +9952,7 @@
         <v>Automated</v>
       </c>
       <c r="L246" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="247">
@@ -9978,7 +9978,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H247" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I247" t="str">
         <v>Medium</v>
@@ -9990,7 +9990,7 @@
         <v>Automated</v>
       </c>
       <c r="L247" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="248">
@@ -10054,7 +10054,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H249" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I249" t="str">
         <v>Medium</v>
@@ -10066,7 +10066,7 @@
         <v>Automated</v>
       </c>
       <c r="L249" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="250">
@@ -10092,7 +10092,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H250" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I250" t="str">
         <v>High</v>
@@ -10104,7 +10104,7 @@
         <v>Automated</v>
       </c>
       <c r="L250" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="251">
@@ -10168,7 +10168,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H252" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I252" t="str">
         <v>Medium</v>
@@ -10180,7 +10180,7 @@
         <v>Automated</v>
       </c>
       <c r="L252" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="253">
@@ -10206,7 +10206,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H253" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I253" t="str">
         <v>Medium</v>
@@ -10218,7 +10218,7 @@
         <v>Automated</v>
       </c>
       <c r="L253" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="254">
@@ -10282,7 +10282,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H255" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I255" t="str">
         <v>Medium</v>
@@ -10294,7 +10294,7 @@
         <v>Automated</v>
       </c>
       <c r="L255" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="256">
@@ -10320,7 +10320,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H256" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I256" t="str">
         <v>Medium</v>
@@ -10332,7 +10332,7 @@
         <v>Automated</v>
       </c>
       <c r="L256" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="257">
@@ -10396,7 +10396,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H258" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I258" t="str">
         <v>High</v>
@@ -10408,7 +10408,7 @@
         <v>Automated</v>
       </c>
       <c r="L258" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="259">
@@ -10434,7 +10434,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H259" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I259" t="str">
         <v>Medium</v>
@@ -10446,7 +10446,7 @@
         <v>Automated</v>
       </c>
       <c r="L259" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="260">
@@ -10510,7 +10510,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H261" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I261" t="str">
         <v>Medium</v>
@@ -10522,7 +10522,7 @@
         <v>Automated</v>
       </c>
       <c r="L261" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="262">
@@ -10548,7 +10548,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H262" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I262" t="str">
         <v>High</v>
@@ -10560,7 +10560,7 @@
         <v>Automated</v>
       </c>
       <c r="L262" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="263">
@@ -10624,7 +10624,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H264" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I264" t="str">
         <v>Medium</v>
@@ -10636,7 +10636,7 @@
         <v>Automated</v>
       </c>
       <c r="L264" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="265">
@@ -10662,7 +10662,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H265" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I265" t="str">
         <v>Medium</v>
@@ -10674,7 +10674,7 @@
         <v>Automated</v>
       </c>
       <c r="L265" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="266">
@@ -10738,7 +10738,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H267" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I267" t="str">
         <v>Medium</v>
@@ -10750,7 +10750,7 @@
         <v>Automated</v>
       </c>
       <c r="L267" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="268">
@@ -10776,7 +10776,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H268" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I268" t="str">
         <v>Medium</v>
@@ -10788,7 +10788,7 @@
         <v>Automated</v>
       </c>
       <c r="L268" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="269">
@@ -10852,7 +10852,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H270" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I270" t="str">
         <v>High</v>
@@ -10864,7 +10864,7 @@
         <v>Automated</v>
       </c>
       <c r="L270" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="271">
@@ -10890,7 +10890,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H271" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I271" t="str">
         <v>Medium</v>
@@ -10902,7 +10902,7 @@
         <v>Automated</v>
       </c>
       <c r="L271" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="272">
@@ -10966,7 +10966,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H273" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I273" t="str">
         <v>Medium</v>
@@ -10978,7 +10978,7 @@
         <v>Automated</v>
       </c>
       <c r="L273" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="274">
@@ -11004,7 +11004,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H274" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I274" t="str">
         <v>High</v>
@@ -11016,7 +11016,7 @@
         <v>Automated</v>
       </c>
       <c r="L274" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="275">
@@ -11080,7 +11080,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H276" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I276" t="str">
         <v>Medium</v>
@@ -11092,7 +11092,7 @@
         <v>Automated</v>
       </c>
       <c r="L276" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="277">
@@ -11118,7 +11118,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H277" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I277" t="str">
         <v>Medium</v>
@@ -11130,7 +11130,7 @@
         <v>Automated</v>
       </c>
       <c r="L277" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="278">
@@ -11194,7 +11194,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H279" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I279" t="str">
         <v>Medium</v>
@@ -11206,7 +11206,7 @@
         <v>Automated</v>
       </c>
       <c r="L279" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="280">
@@ -11232,7 +11232,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H280" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I280" t="str">
         <v>Medium</v>
@@ -11244,7 +11244,7 @@
         <v>Automated</v>
       </c>
       <c r="L280" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="281">
@@ -11308,7 +11308,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H282" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I282" t="str">
         <v>High</v>
@@ -11320,7 +11320,7 @@
         <v>Automated</v>
       </c>
       <c r="L282" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="283">
@@ -11346,7 +11346,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H283" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I283" t="str">
         <v>Medium</v>
@@ -11358,7 +11358,7 @@
         <v>Automated</v>
       </c>
       <c r="L283" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="284">
@@ -11422,7 +11422,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H285" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I285" t="str">
         <v>Medium</v>
@@ -11434,7 +11434,7 @@
         <v>Automated</v>
       </c>
       <c r="L285" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="286">
@@ -11460,7 +11460,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H286" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I286" t="str">
         <v>High</v>
@@ -11472,7 +11472,7 @@
         <v>Automated</v>
       </c>
       <c r="L286" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="287">
@@ -11536,7 +11536,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H288" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I288" t="str">
         <v>Medium</v>
@@ -11548,7 +11548,7 @@
         <v>Automated</v>
       </c>
       <c r="L288" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="289">
@@ -11574,7 +11574,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H289" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I289" t="str">
         <v>Medium</v>
@@ -11586,7 +11586,7 @@
         <v>Automated</v>
       </c>
       <c r="L289" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="290">
@@ -11650,7 +11650,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H291" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I291" t="str">
         <v>Medium</v>
@@ -11662,7 +11662,7 @@
         <v>Automated</v>
       </c>
       <c r="L291" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="292">
@@ -11688,7 +11688,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H292" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I292" t="str">
         <v>Medium</v>
@@ -11700,7 +11700,7 @@
         <v>Automated</v>
       </c>
       <c r="L292" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="293">
@@ -11764,7 +11764,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H294" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I294" t="str">
         <v>High</v>
@@ -11776,7 +11776,7 @@
         <v>Automated</v>
       </c>
       <c r="L294" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="295">
@@ -11802,7 +11802,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H295" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I295" t="str">
         <v>Medium</v>
@@ -11814,7 +11814,7 @@
         <v>Automated</v>
       </c>
       <c r="L295" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="296">
@@ -11878,7 +11878,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H297" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I297" t="str">
         <v>Medium</v>
@@ -11890,7 +11890,7 @@
         <v>Automated</v>
       </c>
       <c r="L297" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="298">
@@ -11916,7 +11916,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H298" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I298" t="str">
         <v>High</v>
@@ -11928,7 +11928,7 @@
         <v>Automated</v>
       </c>
       <c r="L298" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="299">
@@ -11992,7 +11992,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H300" t="str">
-        <v>Minor deviation detected</v>
+        <v>Within expected range</v>
       </c>
       <c r="I300" t="str">
         <v>Medium</v>
@@ -12004,7 +12004,7 @@
         <v>Automated</v>
       </c>
       <c r="L300" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="301">
@@ -12030,7 +12030,7 @@
         <v>Throughput and latency remain within acceptable thresholds</v>
       </c>
       <c r="H301" t="str">
-        <v>Not executed</v>
+        <v>Within expected range</v>
       </c>
       <c r="I301" t="str">
         <v>Medium</v>
@@ -12042,12 +12042,3812 @@
         <v>Automated</v>
       </c>
       <c r="L301" t="str">
-        <v>NOT EXECUTED</v>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>LT-1300</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Validate Concurrent Users under baseline load</v>
+      </c>
+      <c r="E302" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F302" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G302" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H302" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I302" t="str">
+        <v>High</v>
+      </c>
+      <c r="J302" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K302" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L302" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>LT-1301</v>
+      </c>
+      <c r="B303" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="C303" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Validate RPS under baseline load</v>
+      </c>
+      <c r="E303" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F303" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G303" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H303" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I303" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J303" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K303" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L303" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>LT-1302</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Validate Average Response Time under baseline load</v>
+      </c>
+      <c r="E304" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F304" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G304" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H304" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I304" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J304" t="str">
+        <v>High</v>
+      </c>
+      <c r="K304" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L304" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>LT-1303</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="C305" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Validate Minimum under baseline load</v>
+      </c>
+      <c r="E305" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F305" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G305" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H305" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I305" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J305" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K305" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L305" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>LT-1304</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="C306" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Validate Maximum under baseline load</v>
+      </c>
+      <c r="E306" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F306" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G306" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H306" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I306" t="str">
+        <v>High</v>
+      </c>
+      <c r="J306" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K306" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L306" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>LT-1305</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="C307" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Validate Latency under baseline load</v>
+      </c>
+      <c r="E307" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F307" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G307" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H307" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I307" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J307" t="str">
+        <v>High</v>
+      </c>
+      <c r="K307" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L307" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>LT-1306</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Validate Throughput under baseline load</v>
+      </c>
+      <c r="E308" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F308" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G308" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H308" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I308" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J308" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K308" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L308" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>LT-1307</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Validate Errors under baseline load</v>
+      </c>
+      <c r="E309" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F309" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G309" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H309" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I309" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J309" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K309" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L309" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>LT-1308</v>
+      </c>
+      <c r="B310" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="C310" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Validate CPU under baseline load</v>
+      </c>
+      <c r="E310" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F310" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G310" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H310" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I310" t="str">
+        <v>High</v>
+      </c>
+      <c r="J310" t="str">
+        <v>High</v>
+      </c>
+      <c r="K310" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L310" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>LT-1309</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="C311" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Validate Memory under baseline load</v>
+      </c>
+      <c r="E311" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F311" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G311" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H311" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I311" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J311" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K311" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L311" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>LT-1310</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Validate Stability under baseline load</v>
+      </c>
+      <c r="E312" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F312" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G312" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H312" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I312" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J312" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K312" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L312" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>LT-1311</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="C313" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Validate Error Handling under baseline load</v>
+      </c>
+      <c r="E313" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F313" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G313" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H313" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I313" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J313" t="str">
+        <v>High</v>
+      </c>
+      <c r="K313" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L313" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>LT-1312</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Validate Authentication under baseline load</v>
+      </c>
+      <c r="E314" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F314" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G314" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H314" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I314" t="str">
+        <v>High</v>
+      </c>
+      <c r="J314" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K314" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L314" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>LT-1313</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Validate Authorization under baseline load</v>
+      </c>
+      <c r="E315" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G315" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H315" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K315" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L315" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>LT-1314</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Validate Performance under baseline load</v>
+      </c>
+      <c r="E316" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G316" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H316" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I316" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J316" t="str">
+        <v>High</v>
+      </c>
+      <c r="K316" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L316" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>LT-1315</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="C317" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Validate Scaling under baseline load</v>
+      </c>
+      <c r="E317" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F317" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G317" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H317" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I317" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J317" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K317" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L317" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>LT-1316</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="C318" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Validate Load Spike under baseline load</v>
+      </c>
+      <c r="E318" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G318" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H318" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I318" t="str">
+        <v>High</v>
+      </c>
+      <c r="J318" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K318" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L318" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>LT-1317</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Validate Session Management under baseline load</v>
+      </c>
+      <c r="E319" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G319" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H319" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I319" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J319" t="str">
+        <v>High</v>
+      </c>
+      <c r="K319" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L319" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>LT-1318</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Validate Data Consistency under baseline load</v>
+      </c>
+      <c r="E320" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G320" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H320" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I320" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J320" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K320" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L320" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>LT-1319</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Validate Timeout Handling under baseline load</v>
+      </c>
+      <c r="E321" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G321" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H321" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I321" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J321" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K321" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L321" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>LT-1320</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Validate Concurrent Users under baseline load</v>
+      </c>
+      <c r="E322" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G322" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H322" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I322" t="str">
+        <v>High</v>
+      </c>
+      <c r="J322" t="str">
+        <v>High</v>
+      </c>
+      <c r="K322" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L322" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>LT-1321</v>
+      </c>
+      <c r="B323" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="C323" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Validate RPS under baseline load</v>
+      </c>
+      <c r="E323" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G323" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H323" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I323" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J323" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K323" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L323" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>LT-1322</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Validate Average Response Time under baseline load</v>
+      </c>
+      <c r="E324" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G324" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H324" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I324" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J324" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K324" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L324" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>LT-1323</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="C325" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Validate Minimum under baseline load</v>
+      </c>
+      <c r="E325" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G325" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H325" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I325" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J325" t="str">
+        <v>High</v>
+      </c>
+      <c r="K325" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L325" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>LT-1324</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Validate Maximum under baseline load</v>
+      </c>
+      <c r="E326" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F326" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G326" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H326" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I326" t="str">
+        <v>High</v>
+      </c>
+      <c r="J326" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K326" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L326" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>LT-1325</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="C327" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Validate Latency under baseline load</v>
+      </c>
+      <c r="E327" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F327" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G327" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H327" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I327" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J327" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K327" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L327" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>LT-1326</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Validate Throughput under baseline load</v>
+      </c>
+      <c r="E328" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F328" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G328" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H328" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I328" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J328" t="str">
+        <v>High</v>
+      </c>
+      <c r="K328" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L328" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>LT-1327</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="C329" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Validate Errors under baseline load</v>
+      </c>
+      <c r="E329" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F329" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G329" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H329" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I329" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J329" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K329" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L329" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>LT-1328</v>
+      </c>
+      <c r="B330" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="C330" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Validate CPU under baseline load</v>
+      </c>
+      <c r="E330" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F330" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G330" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H330" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I330" t="str">
+        <v>High</v>
+      </c>
+      <c r="J330" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K330" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L330" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>LT-1329</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="C331" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Validate Memory under baseline load</v>
+      </c>
+      <c r="E331" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F331" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G331" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H331" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I331" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J331" t="str">
+        <v>High</v>
+      </c>
+      <c r="K331" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L331" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>LT-1330</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="D332" t="str">
+        <v>Validate Stability under baseline load</v>
+      </c>
+      <c r="E332" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F332" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G332" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H332" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I332" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J332" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K332" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L332" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>LT-1331</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="C333" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Validate Error Handling under baseline load</v>
+      </c>
+      <c r="E333" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F333" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G333" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H333" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I333" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J333" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K333" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L333" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>LT-1332</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C334" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Validate Authentication under baseline load</v>
+      </c>
+      <c r="E334" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F334" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G334" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H334" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I334" t="str">
+        <v>High</v>
+      </c>
+      <c r="J334" t="str">
+        <v>High</v>
+      </c>
+      <c r="K334" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L334" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>LT-1333</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C335" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Validate Authorization under baseline load</v>
+      </c>
+      <c r="E335" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G335" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H335" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I335" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J335" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K335" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L335" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>LT-1334</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Validate Performance under baseline load</v>
+      </c>
+      <c r="E336" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F336" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G336" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H336" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I336" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J336" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K336" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L336" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>LT-1335</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="C337" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Validate Scaling under baseline load</v>
+      </c>
+      <c r="E337" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F337" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G337" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H337" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I337" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J337" t="str">
+        <v>High</v>
+      </c>
+      <c r="K337" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L337" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>LT-1336</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="C338" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Validate Load Spike under baseline load</v>
+      </c>
+      <c r="E338" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F338" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G338" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H338" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I338" t="str">
+        <v>High</v>
+      </c>
+      <c r="J338" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K338" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L338" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>LT-1337</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="C339" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Validate Session Management under baseline load</v>
+      </c>
+      <c r="E339" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F339" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G339" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H339" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I339" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J339" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K339" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L339" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>LT-1338</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="C340" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Validate Data Consistency under baseline load</v>
+      </c>
+      <c r="E340" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F340" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G340" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H340" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I340" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J340" t="str">
+        <v>High</v>
+      </c>
+      <c r="K340" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L340" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>LT-1339</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="C341" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Validate Timeout Handling under baseline load</v>
+      </c>
+      <c r="E341" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G341" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H341" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I341" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J341" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K341" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L341" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>LT-1340</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Validate Concurrent Users under baseline load</v>
+      </c>
+      <c r="E342" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G342" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H342" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I342" t="str">
+        <v>High</v>
+      </c>
+      <c r="J342" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K342" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L342" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>LT-1341</v>
+      </c>
+      <c r="B343" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="C343" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Validate RPS under baseline load</v>
+      </c>
+      <c r="E343" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G343" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H343" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I343" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J343" t="str">
+        <v>High</v>
+      </c>
+      <c r="K343" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L343" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>LT-1342</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Validate Average Response Time under baseline load</v>
+      </c>
+      <c r="E344" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G344" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H344" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I344" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J344" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K344" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L344" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>LT-1343</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Validate Minimum under baseline load</v>
+      </c>
+      <c r="E345" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G345" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H345" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I345" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J345" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K345" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L345" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>LT-1344</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Validate Maximum under baseline load</v>
+      </c>
+      <c r="E346" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G346" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H346" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I346" t="str">
+        <v>High</v>
+      </c>
+      <c r="J346" t="str">
+        <v>High</v>
+      </c>
+      <c r="K346" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L346" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>LT-1345</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Validate Latency under baseline load</v>
+      </c>
+      <c r="E347" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G347" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H347" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I347" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J347" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K347" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L347" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>LT-1346</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Validate Throughput under baseline load</v>
+      </c>
+      <c r="E348" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F348" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G348" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H348" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I348" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J348" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K348" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L348" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>LT-1347</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Validate Errors under baseline load</v>
+      </c>
+      <c r="E349" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F349" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G349" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H349" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I349" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J349" t="str">
+        <v>High</v>
+      </c>
+      <c r="K349" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L349" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>LT-1348</v>
+      </c>
+      <c r="B350" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="C350" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Validate CPU under baseline load</v>
+      </c>
+      <c r="E350" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F350" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G350" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H350" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I350" t="str">
+        <v>High</v>
+      </c>
+      <c r="J350" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K350" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L350" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>LT-1349</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="C351" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Validate Memory under baseline load</v>
+      </c>
+      <c r="E351" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F351" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G351" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H351" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I351" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J351" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K351" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L351" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>LT-1350</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Validate Stability under baseline load</v>
+      </c>
+      <c r="E352" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F352" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G352" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H352" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I352" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J352" t="str">
+        <v>High</v>
+      </c>
+      <c r="K352" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L352" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>LT-1351</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Validate Error Handling under baseline load</v>
+      </c>
+      <c r="E353" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F353" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G353" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H353" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I353" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J353" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K353" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L353" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>LT-1352</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Validate Authentication under baseline load</v>
+      </c>
+      <c r="E354" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F354" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G354" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H354" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I354" t="str">
+        <v>High</v>
+      </c>
+      <c r="J354" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K354" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L354" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>LT-1353</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="D355" t="str">
+        <v>Validate Authorization under baseline load</v>
+      </c>
+      <c r="E355" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F355" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G355" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H355" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I355" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J355" t="str">
+        <v>High</v>
+      </c>
+      <c r="K355" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L355" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>LT-1354</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Validate Performance under baseline load</v>
+      </c>
+      <c r="E356" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F356" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G356" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H356" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I356" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J356" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K356" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L356" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>LT-1355</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="D357" t="str">
+        <v>Validate Scaling under baseline load</v>
+      </c>
+      <c r="E357" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F357" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G357" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H357" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I357" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J357" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K357" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L357" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>LT-1356</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Validate Load Spike under baseline load</v>
+      </c>
+      <c r="E358" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F358" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G358" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H358" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I358" t="str">
+        <v>High</v>
+      </c>
+      <c r="J358" t="str">
+        <v>High</v>
+      </c>
+      <c r="K358" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L358" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>LT-1357</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="C359" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="D359" t="str">
+        <v>Validate Session Management under baseline load</v>
+      </c>
+      <c r="E359" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F359" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G359" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H359" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I359" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J359" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K359" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L359" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>LT-1358</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Validate Data Consistency under baseline load</v>
+      </c>
+      <c r="E360" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F360" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G360" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H360" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I360" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J360" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K360" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L360" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>LT-1359</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="C361" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Validate Timeout Handling under baseline load</v>
+      </c>
+      <c r="E361" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F361" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G361" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H361" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I361" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J361" t="str">
+        <v>High</v>
+      </c>
+      <c r="K361" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L361" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>LT-1360</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Validate Concurrent Users under baseline load</v>
+      </c>
+      <c r="E362" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F362" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G362" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H362" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I362" t="str">
+        <v>High</v>
+      </c>
+      <c r="J362" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K362" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L362" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>LT-1361</v>
+      </c>
+      <c r="B363" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="C363" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Validate RPS under baseline load</v>
+      </c>
+      <c r="E363" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F363" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G363" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H363" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I363" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J363" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K363" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L363" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>LT-1362</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Validate Average Response Time under baseline load</v>
+      </c>
+      <c r="E364" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F364" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G364" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H364" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I364" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J364" t="str">
+        <v>High</v>
+      </c>
+      <c r="K364" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L364" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>LT-1363</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="C365" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Validate Minimum under baseline load</v>
+      </c>
+      <c r="E365" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F365" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G365" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H365" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I365" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J365" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K365" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L365" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>LT-1364</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="C366" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Validate Maximum under baseline load</v>
+      </c>
+      <c r="E366" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F366" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G366" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H366" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I366" t="str">
+        <v>High</v>
+      </c>
+      <c r="J366" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K366" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L366" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>LT-1365</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="C367" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="D367" t="str">
+        <v>Validate Latency under baseline load</v>
+      </c>
+      <c r="E367" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F367" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G367" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H367" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I367" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J367" t="str">
+        <v>High</v>
+      </c>
+      <c r="K367" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L367" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>LT-1366</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Validate Throughput under baseline load</v>
+      </c>
+      <c r="E368" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F368" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G368" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H368" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I368" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J368" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K368" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L368" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>LT-1367</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="C369" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="D369" t="str">
+        <v>Validate Errors under baseline load</v>
+      </c>
+      <c r="E369" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F369" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G369" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H369" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I369" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J369" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K369" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L369" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>LT-1368</v>
+      </c>
+      <c r="B370" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="C370" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Validate CPU under baseline load</v>
+      </c>
+      <c r="E370" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F370" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G370" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H370" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I370" t="str">
+        <v>High</v>
+      </c>
+      <c r="J370" t="str">
+        <v>High</v>
+      </c>
+      <c r="K370" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L370" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>LT-1369</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="C371" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="D371" t="str">
+        <v>Validate Memory under baseline load</v>
+      </c>
+      <c r="E371" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F371" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G371" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H371" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I371" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J371" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K371" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L371" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>LT-1370</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Validate Stability under baseline load</v>
+      </c>
+      <c r="E372" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F372" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G372" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H372" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I372" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J372" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K372" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L372" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>LT-1371</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="C373" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="D373" t="str">
+        <v>Validate Error Handling under baseline load</v>
+      </c>
+      <c r="E373" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F373" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G373" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H373" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I373" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J373" t="str">
+        <v>High</v>
+      </c>
+      <c r="K373" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L373" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>LT-1372</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Validate Authentication under baseline load</v>
+      </c>
+      <c r="E374" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F374" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G374" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H374" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I374" t="str">
+        <v>High</v>
+      </c>
+      <c r="J374" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K374" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L374" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>LT-1373</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C375" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="D375" t="str">
+        <v>Validate Authorization under baseline load</v>
+      </c>
+      <c r="E375" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F375" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G375" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H375" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I375" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J375" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K375" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L375" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>LT-1374</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D376" t="str">
+        <v>Validate Performance under baseline load</v>
+      </c>
+      <c r="E376" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F376" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G376" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H376" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I376" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J376" t="str">
+        <v>High</v>
+      </c>
+      <c r="K376" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L376" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>LT-1375</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="C377" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Validate Scaling under baseline load</v>
+      </c>
+      <c r="E377" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F377" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G377" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H377" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I377" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J377" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K377" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L377" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>LT-1376</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Validate Load Spike under baseline load</v>
+      </c>
+      <c r="E378" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F378" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G378" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H378" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I378" t="str">
+        <v>High</v>
+      </c>
+      <c r="J378" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K378" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L378" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>LT-1377</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Validate Session Management under baseline load</v>
+      </c>
+      <c r="E379" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F379" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G379" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H379" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I379" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J379" t="str">
+        <v>High</v>
+      </c>
+      <c r="K379" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L379" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>LT-1378</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Validate Data Consistency under baseline load</v>
+      </c>
+      <c r="E380" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F380" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G380" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H380" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I380" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J380" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K380" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L380" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>LT-1379</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="C381" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Validate Timeout Handling under baseline load</v>
+      </c>
+      <c r="E381" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F381" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G381" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H381" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I381" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J381" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K381" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L381" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>LT-1380</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="C382" t="str">
+        <v>Concurrent Users</v>
+      </c>
+      <c r="D382" t="str">
+        <v>Validate Concurrent Users under baseline load</v>
+      </c>
+      <c r="E382" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F382" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G382" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H382" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I382" t="str">
+        <v>High</v>
+      </c>
+      <c r="J382" t="str">
+        <v>High</v>
+      </c>
+      <c r="K382" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L382" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>LT-1381</v>
+      </c>
+      <c r="B383" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="C383" t="str">
+        <v>RPS</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Validate RPS under baseline load</v>
+      </c>
+      <c r="E383" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F383" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G383" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H383" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I383" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J383" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K383" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L383" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>LT-1382</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Average Response Time</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Validate Average Response Time under baseline load</v>
+      </c>
+      <c r="E384" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F384" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G384" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H384" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I384" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J384" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K384" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L384" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>LT-1383</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="C385" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="D385" t="str">
+        <v>Validate Minimum under baseline load</v>
+      </c>
+      <c r="E385" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F385" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G385" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H385" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I385" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J385" t="str">
+        <v>High</v>
+      </c>
+      <c r="K385" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L385" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>LT-1384</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="D386" t="str">
+        <v>Validate Maximum under baseline load</v>
+      </c>
+      <c r="E386" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F386" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G386" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H386" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I386" t="str">
+        <v>High</v>
+      </c>
+      <c r="J386" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K386" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L386" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>LT-1385</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="C387" t="str">
+        <v>Latency</v>
+      </c>
+      <c r="D387" t="str">
+        <v>Validate Latency under baseline load</v>
+      </c>
+      <c r="E387" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F387" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G387" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H387" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I387" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J387" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K387" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L387" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>LT-1386</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Throughput</v>
+      </c>
+      <c r="D388" t="str">
+        <v>Validate Throughput under baseline load</v>
+      </c>
+      <c r="E388" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F388" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G388" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H388" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I388" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J388" t="str">
+        <v>High</v>
+      </c>
+      <c r="K388" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L388" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>LT-1387</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="C389" t="str">
+        <v>Errors</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Validate Errors under baseline load</v>
+      </c>
+      <c r="E389" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F389" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G389" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H389" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I389" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J389" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K389" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L389" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>LT-1388</v>
+      </c>
+      <c r="B390" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="C390" t="str">
+        <v>CPU</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Validate CPU under baseline load</v>
+      </c>
+      <c r="E390" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F390" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G390" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H390" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I390" t="str">
+        <v>High</v>
+      </c>
+      <c r="J390" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K390" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L390" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>LT-1389</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="C391" t="str">
+        <v>Memory</v>
+      </c>
+      <c r="D391" t="str">
+        <v>Validate Memory under baseline load</v>
+      </c>
+      <c r="E391" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F391" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G391" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H391" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I391" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J391" t="str">
+        <v>High</v>
+      </c>
+      <c r="K391" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L391" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>LT-1390</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Stability</v>
+      </c>
+      <c r="D392" t="str">
+        <v>Validate Stability under baseline load</v>
+      </c>
+      <c r="E392" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F392" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G392" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H392" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I392" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J392" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K392" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L392" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>LT-1391</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="C393" t="str">
+        <v>Error Handling</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Validate Error Handling under baseline load</v>
+      </c>
+      <c r="E393" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F393" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G393" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H393" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I393" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J393" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K393" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L393" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>LT-1392</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Authentication</v>
+      </c>
+      <c r="D394" t="str">
+        <v>Validate Authentication under baseline load</v>
+      </c>
+      <c r="E394" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F394" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G394" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H394" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I394" t="str">
+        <v>High</v>
+      </c>
+      <c r="J394" t="str">
+        <v>High</v>
+      </c>
+      <c r="K394" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L394" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>LT-1393</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="C395" t="str">
+        <v>Authorization</v>
+      </c>
+      <c r="D395" t="str">
+        <v>Validate Authorization under baseline load</v>
+      </c>
+      <c r="E395" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F395" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G395" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H395" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I395" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J395" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K395" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L395" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>LT-1394</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D396" t="str">
+        <v>Validate Performance under baseline load</v>
+      </c>
+      <c r="E396" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F396" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G396" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H396" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I396" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J396" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K396" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L396" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>LT-1395</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Scaling</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Validate Scaling under baseline load</v>
+      </c>
+      <c r="E397" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F397" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G397" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H397" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I397" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J397" t="str">
+        <v>High</v>
+      </c>
+      <c r="K397" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L397" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>LT-1396</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Load Spike</v>
+      </c>
+      <c r="D398" t="str">
+        <v>Validate Load Spike under baseline load</v>
+      </c>
+      <c r="E398" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F398" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G398" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H398" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I398" t="str">
+        <v>High</v>
+      </c>
+      <c r="J398" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K398" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L398" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>LT-1397</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Session Management</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Validate Session Management under baseline load</v>
+      </c>
+      <c r="E399" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F399" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G399" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H399" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I399" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J399" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K399" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L399" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>LT-1398</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Data Consistency</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Validate Data Consistency under baseline load</v>
+      </c>
+      <c r="E400" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F400" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G400" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H400" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I400" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J400" t="str">
+        <v>High</v>
+      </c>
+      <c r="K400" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L400" t="str">
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>LT-1399</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Timeout Handling</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Validate Timeout Handling under baseline load</v>
+      </c>
+      <c r="E401" t="str">
+        <v>System is running with 100 simulated concurrent users</v>
+      </c>
+      <c r="F401" t="str">
+        <v>Generate load for 60 seconds and capture response metrics</v>
+      </c>
+      <c r="G401" t="str">
+        <v>Throughput and latency remain within acceptable thresholds</v>
+      </c>
+      <c r="H401" t="str">
+        <v>Within expected range</v>
+      </c>
+      <c r="I401" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="J401" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K401" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="L401" t="str">
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L301"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L401"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>12000</v>
+        <v>115803</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>11.96</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>11.96</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>115803</v>
+        <v>133238</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>51.82</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>51.82</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>133238</v>
+        <v>16459</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>45.04</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>251</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>43</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>55</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>81</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>45.04</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>251</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>43</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>55</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>81</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>16459</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>365.85</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>1391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>362</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>436</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>466</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>365.85</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>1391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>362</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>436</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>466</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/load-test-report.xlsx
+++ b/load-tests/reports/load-test-report.xlsx
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="3">
